--- a/game49/web.xlsx
+++ b/game49/web.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="14280" windowHeight="11730"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="13" r:id="rId1"/>
@@ -66,7 +66,7 @@
     <t>sec.exonerative.site</t>
   </si>
   <si>
-    <t>#b65458</t>
+    <t>#f53d93</t>
   </si>
   <si>
     <t>color</t>
@@ -331,7 +331,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -394,13 +394,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB65458"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4D613C"/>
+        <fgColor rgb="FFF53D93"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF284FEF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24A765"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -721,7 +727,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -745,16 +751,16 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -763,89 +769,89 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -896,6 +902,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1376,7 +1385,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
+      <c r="B7" s="18"/>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
